--- a/evaluation_forms/009_mock_interview_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/009_mock_interview_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -847,8 +847,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -876,12 +876,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'5-6'}</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '5-6'}</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'video_format'}</t>
+          <t>video_format</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Video Format'}</t>
+          <t>Video Format</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'audio_format'}</t>
+          <t>audio_format</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Audio Format'}</t>
+          <t>Audio Format</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'text_format'}</t>
+          <t>text_format</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Text Format'}</t>
+          <t>Text Format</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'15-30_minutes'}</t>
+          <t>15-30_minutes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '15-30 Minutes'}</t>
+          <t>15-30 Minutes</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '30-60 Minutes'}</t>
+          <t>30-60 Minutes</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '1-2 Hours'}</t>
+          <t>1-2 Hours</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'more_than_2_hours'}</t>
+          <t>more_than_2_hours</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'More than 2 Hours'}</t>
+          <t>More than 2 Hours</t>
         </is>
       </c>
     </row>
